--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -1,123 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1F9391-03A5-3248-9370-EDC98640E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="27240" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$30</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>area_type</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>periurban</t>
-  </si>
-  <si>
-    <t>rural</t>
-  </si>
-  <si>
-    <t>urban</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -217,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -251,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -286,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -462,89 +350,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>area_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C2">
-        <v>19509.293000000001</v>
+        <v>20835.383</v>
       </c>
       <c r="D2">
-        <v>18673.638999999999</v>
+        <v>19895.116</v>
       </c>
       <c r="E2">
-        <v>20342.699000000001</v>
+        <v>21773.213</v>
       </c>
       <c r="F2">
-        <v>185393.33799999999</v>
+        <v>189757.658</v>
       </c>
       <c r="G2">
-        <v>181100.03400000001</v>
+        <v>185301.326</v>
       </c>
       <c r="H2">
-        <v>189629.22399999999</v>
+        <v>194260.377</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -556,39 +465,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>24656879688.882999</v>
+        <v>25238524174.864</v>
       </c>
       <c r="M2">
-        <v>24089737440.448002</v>
+        <v>24640427739.445</v>
       </c>
       <c r="N2">
-        <v>25225865688.876999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+        <v>25829487260.422</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C3">
-        <v>18845.974999999999</v>
+        <v>21572.786</v>
       </c>
       <c r="D3">
-        <v>18147.742999999999</v>
+        <v>20764.114</v>
       </c>
       <c r="E3">
-        <v>19536.427</v>
+        <v>22375.597</v>
       </c>
       <c r="F3">
-        <v>177400.03700000001</v>
+        <v>201128.104</v>
       </c>
       <c r="G3">
-        <v>174718.72700000001</v>
+        <v>197701.623</v>
       </c>
       <c r="H3">
-        <v>180027.821</v>
+        <v>204545.206</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -600,39 +513,43 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>23591860969.301998</v>
+        <v>26749534103.462</v>
       </c>
       <c r="M3">
-        <v>23240531183.743</v>
+        <v>26291955964.439</v>
       </c>
       <c r="N3">
-        <v>23946733077.676998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>27211966667.268</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C4">
-        <v>13644.22</v>
+        <v>14166.784</v>
       </c>
       <c r="D4">
-        <v>13163.120999999999</v>
+        <v>13652.581</v>
       </c>
       <c r="E4">
-        <v>14126.472</v>
+        <v>14674.379</v>
       </c>
       <c r="F4">
-        <v>143802.068</v>
+        <v>143914.135</v>
       </c>
       <c r="G4">
-        <v>141537.71</v>
+        <v>141693.687</v>
       </c>
       <c r="H4">
-        <v>146083.48000000001</v>
+        <v>146155.818</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -644,567 +561,619 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>19129725246.076</v>
+        <v>19142768187.06</v>
       </c>
       <c r="M4">
-        <v>18823664147.268002</v>
+        <v>18844892229.808</v>
       </c>
       <c r="N4">
-        <v>19432909804.761002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
+        <v>19439941291.972</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C5">
-        <v>12225</v>
+        <v>12789.155</v>
       </c>
       <c r="D5">
-        <v>11899.494000000001</v>
+        <v>12431.575</v>
       </c>
       <c r="E5">
-        <v>12547.213</v>
+        <v>13147.672</v>
       </c>
       <c r="F5">
-        <v>9997.6860000000015</v>
+        <v>16920.582</v>
       </c>
       <c r="G5">
-        <v>9766.7789999999986</v>
+        <v>16487.709</v>
       </c>
       <c r="H5">
-        <v>10226.117</v>
+        <v>17349.919</v>
       </c>
       <c r="I5">
-        <v>680972788.50399995</v>
+        <v>674113898.4910001</v>
       </c>
       <c r="J5">
-        <v>662904568.64799988</v>
+        <v>655373068.5019999</v>
       </c>
       <c r="K5">
-        <v>699128508.67199993</v>
+        <v>692929903.7729999</v>
       </c>
       <c r="L5">
-        <v>1329844702.1329999</v>
+        <v>2250617329.005</v>
       </c>
       <c r="M5">
-        <v>1299295319.1960001</v>
+        <v>2193786202.342</v>
       </c>
       <c r="N5">
-        <v>1359679294.553</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
+        <v>2307587976.592</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C6">
-        <v>9591.3280000000013</v>
+        <v>11347.274</v>
       </c>
       <c r="D6">
-        <v>9425.6669999999995</v>
+        <v>11133.456</v>
       </c>
       <c r="E6">
-        <v>9757.6619999999984</v>
+        <v>11560.217</v>
       </c>
       <c r="F6">
-        <v>7880.2790000000005</v>
+        <v>15063.129</v>
       </c>
       <c r="G6">
-        <v>7781.686999999999</v>
+        <v>14809.364</v>
       </c>
       <c r="H6">
-        <v>7976.1369999999988</v>
+        <v>15307.87</v>
       </c>
       <c r="I6">
-        <v>534258104.704</v>
+        <v>597956539.046</v>
       </c>
       <c r="J6">
-        <v>524762567.07300001</v>
+        <v>586599853.612</v>
       </c>
       <c r="K6">
-        <v>543478008.55799997</v>
+        <v>609236555.943</v>
       </c>
       <c r="L6">
-        <v>1048270659.398</v>
+        <v>2003370051.762</v>
       </c>
       <c r="M6">
-        <v>1034255717.377</v>
+        <v>1969264270.236</v>
       </c>
       <c r="N6">
-        <v>1060515870.668</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+        <v>2035725318.659</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C7">
-        <v>8302.130000000001</v>
+        <v>7894.636999999999</v>
       </c>
       <c r="D7">
-        <v>8149.4540000000025</v>
+        <v>7749.775000000001</v>
       </c>
       <c r="E7">
-        <v>8454.7909999999974</v>
+        <v>8031.230000000003</v>
       </c>
       <c r="F7">
-        <v>7338.8080000000009</v>
+        <v>10737.362</v>
       </c>
       <c r="G7">
-        <v>7230.6840000000011</v>
+        <v>10568.073</v>
       </c>
       <c r="H7">
-        <v>7445.1339999999982</v>
+        <v>10902.572</v>
       </c>
       <c r="I7">
-        <v>462535922.31300002</v>
+        <v>415928085.528</v>
       </c>
       <c r="J7">
-        <v>453841101.92299992</v>
+        <v>408563380.67</v>
       </c>
       <c r="K7">
-        <v>471174495.07399988</v>
+        <v>423227484.9480001</v>
       </c>
       <c r="L7">
-        <v>975824629.36499977</v>
+        <v>1428017641.991</v>
       </c>
       <c r="M7">
-        <v>962000053.30200005</v>
+        <v>1405810568.373</v>
       </c>
       <c r="N7">
-        <v>989878200.47699976</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>1449749121.724999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C8">
-        <v>5795.0680000000002</v>
+        <v>2260.575</v>
       </c>
       <c r="D8">
-        <v>5798.1729999999998</v>
+        <v>2218.671</v>
       </c>
       <c r="E8">
-        <v>5777.0310000000009</v>
+        <v>2300.544</v>
       </c>
       <c r="F8">
-        <v>7315.1990000000014</v>
+        <v>1033.627</v>
       </c>
       <c r="G8">
-        <v>7346.7379999999994</v>
+        <v>1015.426</v>
       </c>
       <c r="H8">
-        <v>7225.523000000001</v>
+        <v>1050.433</v>
       </c>
       <c r="I8">
-        <v>85813551.796999991</v>
+        <v>66280548.811</v>
       </c>
       <c r="J8">
-        <v>85825047.378999978</v>
+        <v>65003920.82</v>
       </c>
       <c r="K8">
-        <v>85454810.846000001</v>
+        <v>67437918.06999999</v>
       </c>
       <c r="L8">
-        <v>973034696.42400002</v>
+        <v>137470085.716</v>
       </c>
       <c r="M8">
-        <v>977361583.51499987</v>
+        <v>135052185.136</v>
       </c>
       <c r="N8">
-        <v>961224868.76000023</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+        <v>139750650.544</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C9">
-        <v>4090.7669999999998</v>
+        <v>1886.741</v>
       </c>
       <c r="D9">
-        <v>4125.3240000000014</v>
+        <v>1863.238</v>
       </c>
       <c r="E9">
-        <v>4042.5920000000001</v>
+        <v>1907.763</v>
       </c>
       <c r="F9">
-        <v>5232.6190000000006</v>
+        <v>858.981</v>
       </c>
       <c r="G9">
-        <v>5287.6919999999991</v>
+        <v>849.451</v>
       </c>
       <c r="H9">
-        <v>5130.6319999999996</v>
+        <v>867.8770000000001</v>
       </c>
       <c r="I9">
-        <v>60606967.633000024</v>
+        <v>55312300.94500001</v>
       </c>
       <c r="J9">
-        <v>61105518.927999988</v>
+        <v>54623252.899</v>
       </c>
       <c r="K9">
-        <v>59888950.206</v>
+        <v>55963430.755</v>
       </c>
       <c r="L9">
-        <v>696415583.06399989</v>
+        <v>114247327.963</v>
       </c>
       <c r="M9">
-        <v>702724229.80299997</v>
+        <v>112966659.712</v>
       </c>
       <c r="N9">
-        <v>683469851.32800007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
+        <v>115409740.819</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C10">
-        <v>3917.3149999999991</v>
+        <v>1378.443</v>
       </c>
       <c r="D10">
-        <v>3982.407999999999</v>
+        <v>1365.278</v>
       </c>
       <c r="E10">
-        <v>3825.474000000002</v>
+        <v>1392.433</v>
       </c>
       <c r="F10">
-        <v>5603.2160000000003</v>
+        <v>641.0149999999999</v>
       </c>
       <c r="G10">
-        <v>5737.7710000000006</v>
+        <v>636.04</v>
       </c>
       <c r="H10">
-        <v>5411.4459999999963</v>
+        <v>645.9950000000003</v>
       </c>
       <c r="I10">
-        <v>57967787.460999973</v>
+        <v>40428910.54399998</v>
       </c>
       <c r="J10">
-        <v>59018929.585000008</v>
+        <v>40046603.01499999</v>
       </c>
       <c r="K10">
-        <v>56623329.311000019</v>
+        <v>40820598.14</v>
       </c>
       <c r="L10">
-        <v>745123278.07999992</v>
+        <v>85236009.58999997</v>
       </c>
       <c r="M10">
-        <v>763131959.88000011</v>
+        <v>84533159.90200001</v>
       </c>
       <c r="N10">
-        <v>718669294.72900009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
+        <v>85942213.14600003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C11">
-        <v>1342.347</v>
+        <v>1313.664</v>
       </c>
       <c r="D11">
-        <v>1335.412</v>
+        <v>1295.354</v>
       </c>
       <c r="E11">
-        <v>1344.9929999999999</v>
+        <v>1331.443</v>
       </c>
       <c r="F11">
-        <v>2354.6260000000002</v>
+        <v>2704.907</v>
       </c>
       <c r="G11">
-        <v>2342.195999999999</v>
+        <v>2659.941</v>
       </c>
       <c r="H11">
-        <v>2363.049</v>
+        <v>2747.054</v>
       </c>
       <c r="I11">
-        <v>100938754.207</v>
+        <v>51493011.222</v>
       </c>
       <c r="J11">
-        <v>100471617.177</v>
+        <v>50769424.133</v>
       </c>
       <c r="K11">
-        <v>101189032.54700001</v>
+        <v>52205582.163</v>
       </c>
       <c r="L11">
-        <v>313182030.58899999</v>
+        <v>359747314.703</v>
       </c>
       <c r="M11">
-        <v>311509148.82800001</v>
+        <v>353780597.648</v>
       </c>
       <c r="N11">
-        <v>314104775.19300002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>365325277.332</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C12">
-        <v>968.45700000000011</v>
+        <v>1135.148</v>
       </c>
       <c r="D12">
-        <v>972.56</v>
+        <v>1125.151</v>
       </c>
       <c r="E12">
-        <v>959.44200000000001</v>
+        <v>1145.198</v>
       </c>
       <c r="F12">
-        <v>1719.3209999999999</v>
+        <v>2280.413</v>
       </c>
       <c r="G12">
-        <v>1729.978000000001</v>
+        <v>2255.728</v>
       </c>
       <c r="H12">
-        <v>1703.296</v>
+        <v>2302.264000000001</v>
       </c>
       <c r="I12">
-        <v>72803132.083999991</v>
+        <v>44500843.909</v>
       </c>
       <c r="J12">
-        <v>73137005.201999992</v>
+        <v>44099372.55599999</v>
       </c>
       <c r="K12">
-        <v>72269620.848999992</v>
+        <v>44887753.73199999</v>
       </c>
       <c r="L12">
-        <v>228738049.38499999</v>
+        <v>303262881.674</v>
       </c>
       <c r="M12">
-        <v>229848161.78299999</v>
+        <v>300052220.211</v>
       </c>
       <c r="N12">
-        <v>226438866.685</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
+        <v>306178955.787</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C13">
-        <v>1039.9649999999999</v>
+        <v>978.6690000000003</v>
       </c>
       <c r="D13">
-        <v>1051.905999999999</v>
+        <v>972.8210000000004</v>
       </c>
       <c r="E13">
-        <v>1025.278</v>
+        <v>984.2980000000002</v>
       </c>
       <c r="F13">
-        <v>2037.393</v>
+        <v>1756.878</v>
       </c>
       <c r="G13">
-        <v>2066.1950000000002</v>
+        <v>1743.661</v>
       </c>
       <c r="H13">
-        <v>2001.9550000000011</v>
+        <v>1769.563999999999</v>
       </c>
       <c r="I13">
-        <v>78217742.236000031</v>
+        <v>38359004.316</v>
       </c>
       <c r="J13">
-        <v>79250134.388000011</v>
+        <v>38127511.973</v>
       </c>
       <c r="K13">
-        <v>77094655.5</v>
+        <v>38578780.35599999</v>
       </c>
       <c r="L13">
-        <v>271034234.59499991</v>
+        <v>233663192.603</v>
       </c>
       <c r="M13">
-        <v>274825585.2980001</v>
+        <v>231830799.748</v>
       </c>
       <c r="N13">
-        <v>266337777.71899989</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+        <v>235419226.8790001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C14">
-        <v>4184.8050000000003</v>
+        <v>4596.712</v>
       </c>
       <c r="D14">
-        <v>4031.0410000000002</v>
+        <v>4412.977000000001</v>
       </c>
       <c r="E14">
-        <v>4339.5029999999997</v>
+        <v>4781.218999999999</v>
       </c>
       <c r="F14">
-        <v>6568.5510000000004</v>
+        <v>5245.571000000001</v>
       </c>
       <c r="G14">
-        <v>6387.6799999999994</v>
+        <v>5030.637000000001</v>
       </c>
       <c r="H14">
-        <v>6746.3579999999993</v>
+        <v>5459.864999999999</v>
       </c>
       <c r="I14">
-        <v>70481394.087000012</v>
+        <v>76539993.62</v>
       </c>
       <c r="J14">
-        <v>67901362.92400001</v>
+        <v>73484283.148</v>
       </c>
       <c r="K14">
-        <v>73072534.557000011</v>
+        <v>79583120.92299999</v>
       </c>
       <c r="L14">
-        <v>873354560.84499991</v>
+        <v>697742185.1469998</v>
       </c>
       <c r="M14">
-        <v>849336922.26300001</v>
+        <v>668766167.11</v>
       </c>
       <c r="N14">
-        <v>897261840.97799993</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
+        <v>726300911.3089999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C15">
-        <v>3292.027</v>
+        <v>3931.415</v>
       </c>
       <c r="D15">
-        <v>3194.3510000000001</v>
+        <v>3813.095</v>
       </c>
       <c r="E15">
-        <v>3387.1439999999998</v>
+        <v>4048.952</v>
       </c>
       <c r="F15">
-        <v>4836.26</v>
+        <v>4481.973</v>
       </c>
       <c r="G15">
-        <v>4756.2539999999999</v>
+        <v>4341.885</v>
       </c>
       <c r="H15">
-        <v>4914.4670000000006</v>
+        <v>4619.691</v>
       </c>
       <c r="I15">
-        <v>55422453.340999998</v>
+        <v>65451534.753</v>
       </c>
       <c r="J15">
-        <v>53781247.520999998</v>
+        <v>63455662.667</v>
       </c>
       <c r="K15">
-        <v>57044911.550999999</v>
+        <v>67391806.79800001</v>
       </c>
       <c r="L15">
-        <v>643168586.60199988</v>
+        <v>596098220.01</v>
       </c>
       <c r="M15">
-        <v>632323333.9690001</v>
+        <v>577265653.072</v>
       </c>
       <c r="N15">
-        <v>653680524.08099997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
+        <v>614671731.4560001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C16">
-        <v>2713.578</v>
+        <v>2779.069</v>
       </c>
       <c r="D16">
-        <v>2639.0120000000002</v>
+        <v>2696.872</v>
       </c>
       <c r="E16">
-        <v>2789.1150000000011</v>
+        <v>2861.411000000001</v>
       </c>
       <c r="F16">
-        <v>4299.2630000000008</v>
+        <v>3185.895</v>
       </c>
       <c r="G16">
-        <v>4219.875</v>
+        <v>3086.311</v>
       </c>
       <c r="H16">
-        <v>4382.7360000000008</v>
+        <v>3281.811</v>
       </c>
       <c r="I16">
-        <v>45707178.271999978</v>
+        <v>46287393.66099998</v>
       </c>
       <c r="J16">
-        <v>44444321.042000003</v>
+        <v>44921824.243</v>
       </c>
       <c r="K16">
-        <v>46905429.866999999</v>
+        <v>47671001.75</v>
       </c>
       <c r="L16">
-        <v>571812686.03800011</v>
+        <v>423761210.219</v>
       </c>
       <c r="M16">
-        <v>561272100.26300001</v>
+        <v>410558840.849</v>
       </c>
       <c r="N16">
-        <v>582756223.20299983</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
+        <v>436692689.3599999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C17">
-        <v>30257.584999999999</v>
+        <v>26341.858</v>
       </c>
       <c r="D17">
-        <v>29657.554</v>
+        <v>26093.054</v>
       </c>
       <c r="E17">
-        <v>30805.107</v>
+        <v>26596.404</v>
       </c>
       <c r="F17">
-        <v>8402.9619999999995</v>
+        <v>8245.957</v>
       </c>
       <c r="G17">
-        <v>8161.5639999999994</v>
+        <v>8144.916000000001</v>
       </c>
       <c r="H17">
-        <v>8598.3750000000018</v>
+        <v>8342.544</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1216,39 +1185,43 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1117761026.4389999</v>
+        <v>1096700461.411</v>
       </c>
       <c r="M17">
-        <v>1085110887.154</v>
+        <v>1083183784.994</v>
       </c>
       <c r="N17">
-        <v>1142093011.2190001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
+        <v>1109868073.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C18">
-        <v>21891.021000000001</v>
+        <v>21743.354</v>
       </c>
       <c r="D18">
-        <v>21558.294999999998</v>
+        <v>21612.068</v>
       </c>
       <c r="E18">
-        <v>22196.776999999998</v>
+        <v>21869.816</v>
       </c>
       <c r="F18">
-        <v>6088.4169999999986</v>
+        <v>6834.768</v>
       </c>
       <c r="G18">
-        <v>5956.4250000000002</v>
+        <v>6777.27</v>
       </c>
       <c r="H18">
-        <v>6210.3810000000012</v>
+        <v>6889.298999999999</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1260,39 +1233,43 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>809768480.80900013</v>
+        <v>909053341.9170001</v>
       </c>
       <c r="M18">
-        <v>793081378.83500004</v>
+        <v>901508557.8199999</v>
       </c>
       <c r="N18">
-        <v>825725171.51900005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
+        <v>916098899.063</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C19">
-        <v>31507.387999999992</v>
+        <v>21003.86</v>
       </c>
       <c r="D19">
-        <v>30962.791000000001</v>
+        <v>20938.94100000001</v>
       </c>
       <c r="E19">
-        <v>32024.992999999999</v>
+        <v>21073.56300000001</v>
       </c>
       <c r="F19">
-        <v>10096.279</v>
+        <v>7894.954999999998</v>
       </c>
       <c r="G19">
-        <v>9853.6449999999968</v>
+        <v>7842.642999999996</v>
       </c>
       <c r="H19">
-        <v>10332.617</v>
+        <v>7944.358</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1304,171 +1281,187 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>1342758615.5999999</v>
+        <v>1049952141.839</v>
       </c>
       <c r="M19">
-        <v>1312426403.6340001</v>
+        <v>1043263747.497</v>
       </c>
       <c r="N19">
-        <v>1372926447.717</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
+        <v>1056799769.62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C20">
-        <v>13803.15</v>
+        <v>5525.759</v>
       </c>
       <c r="D20">
-        <v>13905.905000000001</v>
+        <v>5447.187000000002</v>
       </c>
       <c r="E20">
-        <v>13645.09700000002</v>
+        <v>5600.740000000002</v>
       </c>
       <c r="F20">
-        <v>18151.034</v>
+        <v>2533.623</v>
       </c>
       <c r="G20">
-        <v>18372.201000000001</v>
+        <v>2500.916999999999</v>
       </c>
       <c r="H20">
-        <v>17767.600999999999</v>
+        <v>2564.305</v>
       </c>
       <c r="I20">
-        <v>204388306.891</v>
+        <v>162021760.3</v>
       </c>
       <c r="J20">
-        <v>205949495.89199999</v>
+        <v>159673776.734</v>
       </c>
       <c r="K20">
-        <v>201967090.36300009</v>
+        <v>164221946.965</v>
       </c>
       <c r="L20">
-        <v>2414573557.5679989</v>
+        <v>336953423.269</v>
       </c>
       <c r="M20">
-        <v>2443217773.198</v>
+        <v>332552004.75</v>
       </c>
       <c r="N20">
-        <v>2363364014.816999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
+        <v>341102604.5090001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C21">
-        <v>30118.45800000001</v>
+        <v>32031.06599999999</v>
       </c>
       <c r="D21">
-        <v>29474.615000000009</v>
+        <v>31314.806</v>
       </c>
       <c r="E21">
-        <v>30759.666000000001</v>
+        <v>32739.11900000001</v>
       </c>
       <c r="F21">
-        <v>25216.773000000008</v>
+        <v>42721.073</v>
       </c>
       <c r="G21">
-        <v>24779.15</v>
+        <v>41865.146</v>
       </c>
       <c r="H21">
-        <v>25647.387999999999</v>
+        <v>43560.361</v>
       </c>
       <c r="I21">
-        <v>1677766815.5209999</v>
+        <v>1687998523.065001</v>
       </c>
       <c r="J21">
-        <v>1641508237.6440001</v>
+        <v>1650536302.784</v>
       </c>
       <c r="K21">
-        <v>1713781012.3039999</v>
+        <v>1725393944.664001</v>
       </c>
       <c r="L21">
-        <v>3353939990.8959999</v>
+        <v>5682005022.758001</v>
       </c>
       <c r="M21">
-        <v>3295551089.875</v>
+        <v>5568861040.950998</v>
       </c>
       <c r="N21">
-        <v>3410073365.698</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
+        <v>5793062416.976</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C22">
-        <v>10190.41</v>
+        <v>11307.196</v>
       </c>
       <c r="D22">
-        <v>9864.4040000000023</v>
+        <v>10922.944</v>
       </c>
       <c r="E22">
-        <v>10515.762000000001</v>
+        <v>11691.582</v>
       </c>
       <c r="F22">
-        <v>15704.074000000001</v>
+        <v>12913.439</v>
       </c>
       <c r="G22">
-        <v>15363.808999999999</v>
+        <v>12458.833</v>
       </c>
       <c r="H22">
-        <v>16043.561</v>
+        <v>13361.367</v>
       </c>
       <c r="I22">
-        <v>171611025.69999999</v>
+        <v>188278922.0339999</v>
       </c>
       <c r="J22">
-        <v>166126931.48699999</v>
+        <v>181861770.058</v>
       </c>
       <c r="K22">
-        <v>177022875.97499999</v>
+        <v>194645929.471</v>
       </c>
       <c r="L22">
-        <v>2088335833.4849999</v>
+        <v>1717601615.376</v>
       </c>
       <c r="M22">
-        <v>2042932356.4949999</v>
+        <v>1656590661.031</v>
       </c>
       <c r="N22">
-        <v>2133698588.2620001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>1777665332.125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C23">
-        <v>83655.994000000006</v>
+        <v>69089.07199999999</v>
       </c>
       <c r="D23">
-        <v>82178.639999999985</v>
+        <v>68644.06300000002</v>
       </c>
       <c r="E23">
-        <v>85026.877000000008</v>
+        <v>69539.783</v>
       </c>
       <c r="F23">
-        <v>24587.65800000001</v>
+        <v>22975.67999999999</v>
       </c>
       <c r="G23">
-        <v>23971.633999999991</v>
+        <v>22764.82899999999</v>
       </c>
       <c r="H23">
-        <v>25141.373</v>
+        <v>23176.20099999999</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1480,83 +1473,91 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>3270288122.848</v>
+        <v>3055705945.167</v>
       </c>
       <c r="M23">
-        <v>3190618669.6230001</v>
+        <v>3027956090.311001</v>
       </c>
       <c r="N23">
-        <v>3340744630.454999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
+        <v>3082766742.202999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C24">
-        <v>3350.7689999999998</v>
+        <v>3427.481</v>
       </c>
       <c r="D24">
-        <v>3359.8779999999988</v>
+        <v>3393.325999999999</v>
       </c>
       <c r="E24">
-        <v>3329.7130000000011</v>
+        <v>3460.939</v>
       </c>
       <c r="F24">
-        <v>6111.3399999999983</v>
+        <v>6742.198</v>
       </c>
       <c r="G24">
-        <v>6138.3690000000006</v>
+        <v>6659.329999999998</v>
       </c>
       <c r="H24">
-        <v>6068.2999999999993</v>
+        <v>6818.882000000001</v>
       </c>
       <c r="I24">
-        <v>251959628.5270001</v>
+        <v>134352859.447</v>
       </c>
       <c r="J24">
-        <v>252858756.76699999</v>
+        <v>132996308.662</v>
       </c>
       <c r="K24">
-        <v>250553308.89599991</v>
+        <v>135672116.251</v>
       </c>
       <c r="L24">
-        <v>812954314.56900001</v>
+        <v>896673388.9800003</v>
       </c>
       <c r="M24">
-        <v>816182895.90899992</v>
+        <v>885663617.6069999</v>
       </c>
       <c r="N24">
-        <v>806881419.59700012</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
+        <v>906923459.9980001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C25">
-        <v>51999.48799999999</v>
+        <v>56574.95299999999</v>
       </c>
       <c r="D25">
-        <v>49984.502999999997</v>
+        <v>54311.811</v>
       </c>
       <c r="E25">
-        <v>54005.598000000013</v>
+        <v>58823.18899999999</v>
       </c>
       <c r="F25">
-        <v>506595.44300000003</v>
+        <v>534799.8970000001</v>
       </c>
       <c r="G25">
-        <v>497356.47100000008</v>
+        <v>524696.6359999999</v>
       </c>
       <c r="H25">
-        <v>515740.52499999991</v>
+        <v>544961.401</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1568,237 +1569,256 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>67378465904.261002</v>
+        <v>71130826465.38599</v>
       </c>
       <c r="M25">
-        <v>66153932771.458977</v>
+        <v>69777275933.69202</v>
       </c>
       <c r="N25">
-        <v>68605508571.314987</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
+        <v>72481395219.66202</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C26">
-        <v>73314.097999999998</v>
+        <v>68137.34699999999</v>
       </c>
       <c r="D26">
-        <v>71395.312999999995</v>
+        <v>66346.747</v>
       </c>
       <c r="E26">
-        <v>75156.545999999988</v>
+        <v>69930.49499999997</v>
       </c>
       <c r="F26">
-        <v>220032.36199999999</v>
+        <v>223908.302</v>
       </c>
       <c r="G26">
-        <v>215104.99100000001</v>
+        <v>218639.955</v>
       </c>
       <c r="H26">
-        <v>224788.64600000001</v>
+        <v>229210.192</v>
       </c>
       <c r="I26">
-        <v>938206488.59499991</v>
+        <v>868427452.1440001</v>
       </c>
       <c r="J26">
-        <v>917102596.1279999</v>
+        <v>844630696.603</v>
       </c>
       <c r="K26">
-        <v>958844886.62199998</v>
+        <v>892156524.9289999</v>
       </c>
       <c r="L26">
-        <v>29264056705.313011</v>
+        <v>29780801550.84601</v>
       </c>
       <c r="M26">
-        <v>28612351301.403999</v>
+        <v>29074996676.675</v>
       </c>
       <c r="N26">
-        <v>29900229479.580002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
+        <v>30478320149.719</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C27">
-        <v>58679.574999999997</v>
+        <v>61616.71799999999</v>
       </c>
       <c r="D27">
-        <v>57423.94</v>
+        <v>60311.12199999999</v>
       </c>
       <c r="E27">
-        <v>59880.043999999987</v>
+        <v>62907.54299999999</v>
       </c>
       <c r="F27">
-        <v>203156.93299999999</v>
+        <v>230647.368</v>
       </c>
       <c r="G27">
-        <v>200230.76300000001</v>
+        <v>226735.3210000001</v>
       </c>
       <c r="H27">
-        <v>205962.73399999991</v>
+        <v>234532.207</v>
       </c>
       <c r="I27">
-        <v>723090657.76199996</v>
+        <v>763221218.6529999</v>
       </c>
       <c r="J27">
-        <v>712786338.72399998</v>
+        <v>748778141.734</v>
       </c>
       <c r="K27">
-        <v>732681491.16399992</v>
+        <v>777479547.2279996</v>
       </c>
       <c r="L27">
-        <v>27018222328.560009</v>
+        <v>30675565926.78799</v>
       </c>
       <c r="M27">
-        <v>26632764005.509998</v>
+        <v>30153013325.48999</v>
       </c>
       <c r="N27">
-        <v>27396563361.958</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
+        <v>31200051313.052</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C28">
-        <v>61124.59599999999</v>
+        <v>48201.462</v>
       </c>
       <c r="D28">
-        <v>59948.691999999981</v>
+        <v>47376.268</v>
       </c>
       <c r="E28">
-        <v>62246.122999999992</v>
+        <v>49017.31399999998</v>
       </c>
       <c r="F28">
-        <v>173177.0269999998</v>
+        <v>168130.24</v>
       </c>
       <c r="G28">
-        <v>170645.88</v>
+        <v>165570.415</v>
       </c>
       <c r="H28">
-        <v>175657.3680000001</v>
+        <v>170700.118</v>
       </c>
       <c r="I28">
-        <v>644428630.28200006</v>
+        <v>541003394.0489998</v>
       </c>
       <c r="J28">
-        <v>636554486.93799996</v>
+        <v>531659319.9010003</v>
       </c>
       <c r="K28">
-        <v>651797909.75199986</v>
+        <v>550297865.194</v>
       </c>
       <c r="L28">
-        <v>23036278689.754009</v>
+        <v>22363398383.302</v>
       </c>
       <c r="M28">
-        <v>22697320249.645</v>
+        <v>22020889346.177</v>
       </c>
       <c r="N28">
-        <v>23363477748.605999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
+        <v>22704544312.702</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C29">
-        <v>193118.26899999991</v>
+        <v>177955.527</v>
       </c>
       <c r="D29">
-        <v>188767.94499999989</v>
+        <v>174034.137</v>
       </c>
       <c r="E29">
-        <v>197282.7129999999</v>
+        <v>181855.3520000001</v>
       </c>
       <c r="F29">
-        <v>596366.32200000004</v>
+        <v>622685.9099999995</v>
       </c>
       <c r="G29">
-        <v>585981.63399999973</v>
+        <v>610945.691</v>
       </c>
       <c r="H29">
-        <v>606408.74800000002</v>
+        <v>634442.517</v>
       </c>
       <c r="I29">
-        <v>2305725776.6389999</v>
+        <v>2172652064.846002</v>
       </c>
       <c r="J29">
-        <v>2266443421.789999</v>
+        <v>2125068158.237999</v>
       </c>
       <c r="K29">
-        <v>2343324287.5379992</v>
+        <v>2219933937.351001</v>
       </c>
       <c r="L29">
-        <v>79318557723.627014</v>
+        <v>82819765860.93596</v>
       </c>
       <c r="M29">
-        <v>77942435556.559097</v>
+        <v>81248899348.34198</v>
       </c>
       <c r="N29">
-        <v>80660270590.144012</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
+        <v>84382915775.47302</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chronic diseases</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C30">
-        <v>141118.78099999999</v>
+        <v>95607.64199999999</v>
       </c>
       <c r="D30">
-        <v>138783.44200000001</v>
+        <v>93454.44499999999</v>
       </c>
       <c r="E30">
-        <v>143277.11499999999</v>
+        <v>97737.79300000003</v>
       </c>
       <c r="F30">
-        <v>89770.879000000015</v>
+        <v>272873.2050000001</v>
       </c>
       <c r="G30">
-        <v>88625.163</v>
+        <v>267963.1190000001</v>
       </c>
       <c r="H30">
-        <v>90668.223000000115</v>
+        <v>277739.42</v>
       </c>
       <c r="I30">
-        <v>2305725776.6389999</v>
+        <v>2172652064.846002</v>
       </c>
       <c r="J30">
-        <v>2266443421.789999</v>
+        <v>2125068158.237999</v>
       </c>
       <c r="K30">
-        <v>2343324287.5379992</v>
+        <v>2219933937.351001</v>
       </c>
       <c r="L30">
-        <v>11940091819.365999</v>
+        <v>36291820895.762</v>
       </c>
       <c r="M30">
-        <v>11788502785.1</v>
+        <v>35637131846.59799</v>
       </c>
       <c r="N30">
-        <v>12054762018.829</v>
+        <v>36946819379.939</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -1782,22 +1782,22 @@
         </is>
       </c>
       <c r="C30">
-        <v>95607.64199999999</v>
+        <v>52291.50199999999</v>
       </c>
       <c r="D30">
-        <v>93454.44499999999</v>
+        <v>51078.26299999999</v>
       </c>
       <c r="E30">
-        <v>97737.79300000003</v>
+        <v>53492.37999999999</v>
       </c>
       <c r="F30">
-        <v>272873.2050000001</v>
+        <v>64910.33300000003</v>
       </c>
       <c r="G30">
-        <v>267963.1190000001</v>
+        <v>63484.226</v>
       </c>
       <c r="H30">
-        <v>277739.42</v>
+        <v>66304.91500000002</v>
       </c>
       <c r="I30">
         <v>2172652064.846002</v>
@@ -1809,13 +1809,13 @@
         <v>2219933937.351001</v>
       </c>
       <c r="L30">
-        <v>36291820895.762</v>
+        <v>8633233450.382999</v>
       </c>
       <c r="M30">
-        <v>35637131846.59799</v>
+        <v>8443667324.338997</v>
       </c>
       <c r="N30">
-        <v>36946819379.939</v>
+        <v>8818753813.608</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_added_1000replicate.xlsx
@@ -1,21 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57798E31-9A02-D44E-B539-145AEA8A3640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="28560" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Chronic diseases</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +149,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +201,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +235,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +270,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,98 +446,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>20835.383</v>
+        <v>20835.383000000002</v>
       </c>
       <c r="D2">
-        <v>19895.116</v>
+        <v>19895.116000000002</v>
       </c>
       <c r="E2">
         <v>21773.213</v>
@@ -453,7 +528,7 @@
         <v>185301.326</v>
       </c>
       <c r="H2">
-        <v>194260.377</v>
+        <v>194260.37700000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,43 +540,39 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>25238524174.864</v>
+        <v>25238524174.863998</v>
       </c>
       <c r="M2">
         <v>24640427739.445</v>
       </c>
       <c r="N2">
-        <v>25829487260.422</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>25829487260.422001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
         <v>21572.786</v>
       </c>
       <c r="D3">
-        <v>20764.114</v>
+        <v>20764.114000000001</v>
       </c>
       <c r="E3">
-        <v>22375.597</v>
+        <v>22375.597000000002</v>
       </c>
       <c r="F3">
-        <v>201128.104</v>
+        <v>201128.10399999999</v>
       </c>
       <c r="G3">
-        <v>197701.623</v>
+        <v>197701.62299999999</v>
       </c>
       <c r="H3">
-        <v>204545.206</v>
+        <v>204545.20600000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,25 +584,21 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>26749534103.462</v>
+        <v>26749534103.462002</v>
       </c>
       <c r="M3">
-        <v>26291955964.439</v>
+        <v>26291955964.438999</v>
       </c>
       <c r="N3">
-        <v>27211966667.268</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>27211966667.268002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>14166.784</v>
@@ -540,13 +607,13 @@
         <v>13652.581</v>
       </c>
       <c r="E4">
-        <v>14674.379</v>
+        <v>14674.379000000001</v>
       </c>
       <c r="F4">
-        <v>143914.135</v>
+        <v>143914.13500000001</v>
       </c>
       <c r="G4">
-        <v>141693.687</v>
+        <v>141693.68700000001</v>
       </c>
       <c r="H4">
         <v>146155.818</v>
@@ -561,55 +628,51 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>19142768187.06</v>
+        <v>19142768187.060001</v>
       </c>
       <c r="M4">
-        <v>18844892229.808</v>
+        <v>18844892229.807999</v>
       </c>
       <c r="N4">
         <v>19439941291.972</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>12789.155</v>
+        <v>12789.155000000001</v>
       </c>
       <c r="D5">
-        <v>12431.575</v>
+        <v>12431.575000000001</v>
       </c>
       <c r="E5">
         <v>13147.672</v>
       </c>
       <c r="F5">
-        <v>16920.582</v>
+        <v>16920.581999999999</v>
       </c>
       <c r="G5">
-        <v>16487.709</v>
+        <v>16487.708999999999</v>
       </c>
       <c r="H5">
-        <v>17349.919</v>
+        <v>17349.919000000002</v>
       </c>
       <c r="I5">
-        <v>674113898.4910001</v>
+        <v>674113898.49100006</v>
       </c>
       <c r="J5">
-        <v>655373068.5019999</v>
+        <v>655373068.50199986</v>
       </c>
       <c r="K5">
-        <v>692929903.7729999</v>
+        <v>692929903.77299988</v>
       </c>
       <c r="L5">
-        <v>2250617329.005</v>
+        <v>2250617329.0050001</v>
       </c>
       <c r="M5">
         <v>2193786202.342</v>
@@ -618,28 +681,24 @@
         <v>2307587976.592</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>11347.274</v>
+        <v>11347.273999999999</v>
       </c>
       <c r="D6">
         <v>11133.456</v>
       </c>
       <c r="E6">
-        <v>11560.217</v>
+        <v>11560.217000000001</v>
       </c>
       <c r="F6">
-        <v>15063.129</v>
+        <v>15063.129000000001</v>
       </c>
       <c r="G6">
         <v>14809.364</v>
@@ -651,43 +710,39 @@
         <v>597956539.046</v>
       </c>
       <c r="J6">
-        <v>586599853.612</v>
+        <v>586599853.61199999</v>
       </c>
       <c r="K6">
-        <v>609236555.943</v>
+        <v>609236555.94299996</v>
       </c>
       <c r="L6">
-        <v>2003370051.762</v>
+        <v>2003370051.7620001</v>
       </c>
       <c r="M6">
-        <v>1969264270.236</v>
+        <v>1969264270.2360001</v>
       </c>
       <c r="N6">
-        <v>2035725318.659</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>2035725318.6589999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>7894.636999999999</v>
+        <v>7894.6369999999988</v>
       </c>
       <c r="D7">
-        <v>7749.775000000001</v>
+        <v>7749.7750000000005</v>
       </c>
       <c r="E7">
-        <v>8031.230000000003</v>
+        <v>8031.2300000000032</v>
       </c>
       <c r="F7">
-        <v>10737.362</v>
+        <v>10737.361999999999</v>
       </c>
       <c r="G7">
         <v>10568.073</v>
@@ -699,40 +754,36 @@
         <v>415928085.528</v>
       </c>
       <c r="J7">
-        <v>408563380.67</v>
+        <v>408563380.67000002</v>
       </c>
       <c r="K7">
-        <v>423227484.9480001</v>
+        <v>423227484.94800007</v>
       </c>
       <c r="L7">
-        <v>1428017641.991</v>
+        <v>1428017641.9909999</v>
       </c>
       <c r="M7">
-        <v>1405810568.373</v>
+        <v>1405810568.3729999</v>
       </c>
       <c r="N7">
         <v>1449749121.724999</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>2260.575</v>
+        <v>2260.5749999999998</v>
       </c>
       <c r="D8">
-        <v>2218.671</v>
+        <v>2218.6709999999998</v>
       </c>
       <c r="E8">
-        <v>2300.544</v>
+        <v>2300.5439999999999</v>
       </c>
       <c r="F8">
         <v>1033.627</v>
@@ -744,61 +795,57 @@
         <v>1050.433</v>
       </c>
       <c r="I8">
-        <v>66280548.811</v>
+        <v>66280548.810999997</v>
       </c>
       <c r="J8">
         <v>65003920.82</v>
       </c>
       <c r="K8">
-        <v>67437918.06999999</v>
+        <v>67437918.069999993</v>
       </c>
       <c r="L8">
-        <v>137470085.716</v>
+        <v>137470085.71599999</v>
       </c>
       <c r="M8">
-        <v>135052185.136</v>
+        <v>135052185.13600001</v>
       </c>
       <c r="N8">
         <v>139750650.544</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
         <v>1886.741</v>
       </c>
       <c r="D9">
-        <v>1863.238</v>
+        <v>1863.2380000000001</v>
       </c>
       <c r="E9">
-        <v>1907.763</v>
+        <v>1907.7629999999999</v>
       </c>
       <c r="F9">
-        <v>858.981</v>
+        <v>858.98099999999999</v>
       </c>
       <c r="G9">
-        <v>849.451</v>
+        <v>849.45100000000002</v>
       </c>
       <c r="H9">
-        <v>867.8770000000001</v>
+        <v>867.87700000000007</v>
       </c>
       <c r="I9">
-        <v>55312300.94500001</v>
+        <v>55312300.945000008</v>
       </c>
       <c r="J9">
-        <v>54623252.899</v>
+        <v>54623252.898999996</v>
       </c>
       <c r="K9">
-        <v>55963430.755</v>
+        <v>55963430.755000003</v>
       </c>
       <c r="L9">
         <v>114247327.963</v>
@@ -807,19 +854,15 @@
         <v>112966659.712</v>
       </c>
       <c r="N9">
-        <v>115409740.819</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>115409740.81900001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>1378.443</v>
@@ -831,43 +874,39 @@
         <v>1392.433</v>
       </c>
       <c r="F10">
-        <v>641.0149999999999</v>
+        <v>641.01499999999987</v>
       </c>
       <c r="G10">
         <v>636.04</v>
       </c>
       <c r="H10">
-        <v>645.9950000000003</v>
+        <v>645.99500000000035</v>
       </c>
       <c r="I10">
-        <v>40428910.54399998</v>
+        <v>40428910.543999977</v>
       </c>
       <c r="J10">
-        <v>40046603.01499999</v>
+        <v>40046603.014999993</v>
       </c>
       <c r="K10">
-        <v>40820598.14</v>
+        <v>40820598.140000001</v>
       </c>
       <c r="L10">
-        <v>85236009.58999997</v>
+        <v>85236009.589999974</v>
       </c>
       <c r="M10">
         <v>84533159.90200001</v>
       </c>
       <c r="N10">
-        <v>85942213.14600003</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>85942213.146000028</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>1313.664</v>
@@ -879,121 +918,113 @@
         <v>1331.443</v>
       </c>
       <c r="F11">
-        <v>2704.907</v>
+        <v>2704.9070000000002</v>
       </c>
       <c r="G11">
-        <v>2659.941</v>
+        <v>2659.9409999999998</v>
       </c>
       <c r="H11">
-        <v>2747.054</v>
+        <v>2747.0540000000001</v>
       </c>
       <c r="I11">
-        <v>51493011.222</v>
+        <v>51493011.222000003</v>
       </c>
       <c r="J11">
-        <v>50769424.133</v>
+        <v>50769424.133000001</v>
       </c>
       <c r="K11">
-        <v>52205582.163</v>
+        <v>52205582.163000003</v>
       </c>
       <c r="L11">
-        <v>359747314.703</v>
+        <v>359747314.70300001</v>
       </c>
       <c r="M11">
         <v>353780597.648</v>
       </c>
       <c r="N11">
-        <v>365325277.332</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>365325277.33200002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>1135.148</v>
+        <v>1135.1479999999999</v>
       </c>
       <c r="D12">
-        <v>1125.151</v>
+        <v>1125.1510000000001</v>
       </c>
       <c r="E12">
-        <v>1145.198</v>
+        <v>1145.1980000000001</v>
       </c>
       <c r="F12">
         <v>2280.413</v>
       </c>
       <c r="G12">
-        <v>2255.728</v>
+        <v>2255.7280000000001</v>
       </c>
       <c r="H12">
         <v>2302.264000000001</v>
       </c>
       <c r="I12">
-        <v>44500843.909</v>
+        <v>44500843.909000002</v>
       </c>
       <c r="J12">
-        <v>44099372.55599999</v>
+        <v>44099372.555999987</v>
       </c>
       <c r="K12">
-        <v>44887753.73199999</v>
+        <v>44887753.731999993</v>
       </c>
       <c r="L12">
-        <v>303262881.674</v>
+        <v>303262881.67400002</v>
       </c>
       <c r="M12">
-        <v>300052220.211</v>
+        <v>300052220.21100003</v>
       </c>
       <c r="N12">
         <v>306178955.787</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>978.6690000000003</v>
+        <v>978.66900000000032</v>
       </c>
       <c r="D13">
-        <v>972.8210000000004</v>
+        <v>972.82100000000037</v>
       </c>
       <c r="E13">
-        <v>984.2980000000002</v>
+        <v>984.29800000000023</v>
       </c>
       <c r="F13">
-        <v>1756.878</v>
+        <v>1756.8779999999999</v>
       </c>
       <c r="G13">
-        <v>1743.661</v>
+        <v>1743.6610000000001</v>
       </c>
       <c r="H13">
-        <v>1769.563999999999</v>
+        <v>1769.5639999999989</v>
       </c>
       <c r="I13">
         <v>38359004.316</v>
       </c>
       <c r="J13">
-        <v>38127511.973</v>
+        <v>38127511.972999997</v>
       </c>
       <c r="K13">
-        <v>38578780.35599999</v>
+        <v>38578780.355999991</v>
       </c>
       <c r="L13">
-        <v>233663192.603</v>
+        <v>233663192.60299999</v>
       </c>
       <c r="M13">
         <v>231830799.748</v>
@@ -1002,118 +1033,106 @@
         <v>235419226.8790001</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>4596.712</v>
+        <v>4596.7120000000004</v>
       </c>
       <c r="D14">
-        <v>4412.977000000001</v>
+        <v>4412.9770000000008</v>
       </c>
       <c r="E14">
-        <v>4781.218999999999</v>
+        <v>4781.2189999999991</v>
       </c>
       <c r="F14">
-        <v>5245.571000000001</v>
+        <v>5245.5710000000008</v>
       </c>
       <c r="G14">
-        <v>5030.637000000001</v>
+        <v>5030.6370000000006</v>
       </c>
       <c r="H14">
-        <v>5459.864999999999</v>
+        <v>5459.8649999999989</v>
       </c>
       <c r="I14">
-        <v>76539993.62</v>
+        <v>76539993.620000005</v>
       </c>
       <c r="J14">
-        <v>73484283.148</v>
+        <v>73484283.148000002</v>
       </c>
       <c r="K14">
-        <v>79583120.92299999</v>
+        <v>79583120.922999993</v>
       </c>
       <c r="L14">
-        <v>697742185.1469998</v>
+        <v>697742185.14699984</v>
       </c>
       <c r="M14">
-        <v>668766167.11</v>
+        <v>668766167.11000001</v>
       </c>
       <c r="N14">
         <v>726300911.3089999</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>3931.415</v>
       </c>
       <c r="D15">
-        <v>3813.095</v>
+        <v>3813.0949999999998</v>
       </c>
       <c r="E15">
-        <v>4048.952</v>
+        <v>4048.9520000000002</v>
       </c>
       <c r="F15">
         <v>4481.973</v>
       </c>
       <c r="G15">
-        <v>4341.885</v>
+        <v>4341.8850000000002</v>
       </c>
       <c r="H15">
-        <v>4619.691</v>
+        <v>4619.6909999999998</v>
       </c>
       <c r="I15">
-        <v>65451534.753</v>
+        <v>65451534.752999999</v>
       </c>
       <c r="J15">
-        <v>63455662.667</v>
+        <v>63455662.667000003</v>
       </c>
       <c r="K15">
-        <v>67391806.79800001</v>
+        <v>67391806.798000008</v>
       </c>
       <c r="L15">
-        <v>596098220.01</v>
+        <v>596098220.00999999</v>
       </c>
       <c r="M15">
-        <v>577265653.072</v>
+        <v>577265653.07200003</v>
       </c>
       <c r="N15">
-        <v>614671731.4560001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>614671731.45600009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
         <v>2779.069</v>
       </c>
       <c r="D16">
-        <v>2696.872</v>
+        <v>2696.8719999999998</v>
       </c>
       <c r="E16">
         <v>2861.411000000001</v>
@@ -1122,40 +1141,36 @@
         <v>3185.895</v>
       </c>
       <c r="G16">
-        <v>3086.311</v>
+        <v>3086.3110000000001</v>
       </c>
       <c r="H16">
-        <v>3281.811</v>
+        <v>3281.8110000000001</v>
       </c>
       <c r="I16">
-        <v>46287393.66099998</v>
+        <v>46287393.660999984</v>
       </c>
       <c r="J16">
-        <v>44921824.243</v>
+        <v>44921824.243000001</v>
       </c>
       <c r="K16">
         <v>47671001.75</v>
       </c>
       <c r="L16">
-        <v>423761210.219</v>
+        <v>423761210.21899998</v>
       </c>
       <c r="M16">
-        <v>410558840.849</v>
+        <v>410558840.84899998</v>
       </c>
       <c r="N16">
         <v>436692689.3599999</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
         <v>26341.858</v>
@@ -1164,16 +1179,16 @@
         <v>26093.054</v>
       </c>
       <c r="E17">
-        <v>26596.404</v>
+        <v>26596.403999999999</v>
       </c>
       <c r="F17">
-        <v>8245.957</v>
+        <v>8245.9570000000003</v>
       </c>
       <c r="G17">
-        <v>8144.916000000001</v>
+        <v>8144.9160000000011</v>
       </c>
       <c r="H17">
-        <v>8342.544</v>
+        <v>8342.5439999999999</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1194,25 +1209,21 @@
         <v>1109868073.52</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>21743.354</v>
+        <v>21743.353999999999</v>
       </c>
       <c r="D18">
-        <v>21612.068</v>
+        <v>21612.067999999999</v>
       </c>
       <c r="E18">
-        <v>21869.816</v>
+        <v>21869.815999999999</v>
       </c>
       <c r="F18">
         <v>6834.768</v>
@@ -1221,7 +1232,7 @@
         <v>6777.27</v>
       </c>
       <c r="H18">
-        <v>6889.298999999999</v>
+        <v>6889.2989999999991</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,25 +1244,21 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>909053341.9170001</v>
+        <v>909053341.91700006</v>
       </c>
       <c r="M18">
-        <v>901508557.8199999</v>
+        <v>901508557.81999993</v>
       </c>
       <c r="N18">
-        <v>916098899.063</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>916098899.06299996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
         <v>21003.86</v>
@@ -1260,16 +1267,16 @@
         <v>20938.94100000001</v>
       </c>
       <c r="E19">
-        <v>21073.56300000001</v>
+        <v>21073.563000000009</v>
       </c>
       <c r="F19">
-        <v>7894.954999999998</v>
+        <v>7894.9549999999981</v>
       </c>
       <c r="G19">
-        <v>7842.642999999996</v>
+        <v>7842.6429999999964</v>
       </c>
       <c r="H19">
-        <v>7944.358</v>
+        <v>7944.3580000000002</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1290,25 +1297,21 @@
         <v>1056799769.62</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
         <v>5525.759</v>
       </c>
       <c r="D20">
-        <v>5447.187000000002</v>
+        <v>5447.1870000000017</v>
       </c>
       <c r="E20">
-        <v>5600.740000000002</v>
+        <v>5600.7400000000016</v>
       </c>
       <c r="F20">
         <v>2533.623</v>
@@ -1317,10 +1320,10 @@
         <v>2500.916999999999</v>
       </c>
       <c r="H20">
-        <v>2564.305</v>
+        <v>2564.3049999999998</v>
       </c>
       <c r="I20">
-        <v>162021760.3</v>
+        <v>162021760.30000001</v>
       </c>
       <c r="J20">
         <v>159673776.734</v>
@@ -1329,28 +1332,24 @@
         <v>164221946.965</v>
       </c>
       <c r="L20">
-        <v>336953423.269</v>
+        <v>336953423.26899999</v>
       </c>
       <c r="M20">
         <v>332552004.75</v>
       </c>
       <c r="N20">
-        <v>341102604.5090001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>341102604.50900012</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>32031.06599999999</v>
+        <v>32031.065999999992</v>
       </c>
       <c r="D21">
         <v>31314.806</v>
@@ -1359,43 +1358,39 @@
         <v>32739.11900000001</v>
       </c>
       <c r="F21">
-        <v>42721.073</v>
+        <v>42721.072999999997</v>
       </c>
       <c r="G21">
-        <v>41865.146</v>
+        <v>41865.146000000001</v>
       </c>
       <c r="H21">
-        <v>43560.361</v>
+        <v>43560.360999999997</v>
       </c>
       <c r="I21">
         <v>1687998523.065001</v>
       </c>
       <c r="J21">
-        <v>1650536302.784</v>
+        <v>1650536302.7839999</v>
       </c>
       <c r="K21">
         <v>1725393944.664001</v>
       </c>
       <c r="L21">
-        <v>5682005022.758001</v>
+        <v>5682005022.7580013</v>
       </c>
       <c r="M21">
-        <v>5568861040.950998</v>
+        <v>5568861040.9509983</v>
       </c>
       <c r="N21">
-        <v>5793062416.976</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5793062416.9759998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
         <v>11307.196</v>
@@ -1410,55 +1405,51 @@
         <v>12913.439</v>
       </c>
       <c r="G22">
-        <v>12458.833</v>
+        <v>12458.833000000001</v>
       </c>
       <c r="H22">
         <v>13361.367</v>
       </c>
       <c r="I22">
-        <v>188278922.0339999</v>
+        <v>188278922.03399989</v>
       </c>
       <c r="J22">
         <v>181861770.058</v>
       </c>
       <c r="K22">
-        <v>194645929.471</v>
+        <v>194645929.47099999</v>
       </c>
       <c r="L22">
-        <v>1717601615.376</v>
+        <v>1717601615.3759999</v>
       </c>
       <c r="M22">
-        <v>1656590661.031</v>
+        <v>1656590661.0309999</v>
       </c>
       <c r="N22">
         <v>1777665332.125</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>69089.07199999999</v>
+        <v>69089.071999999986</v>
       </c>
       <c r="D23">
-        <v>68644.06300000002</v>
+        <v>68644.063000000024</v>
       </c>
       <c r="E23">
-        <v>69539.783</v>
+        <v>69539.782999999996</v>
       </c>
       <c r="F23">
-        <v>22975.67999999999</v>
+        <v>22975.679999999989</v>
       </c>
       <c r="G23">
-        <v>22764.82899999999</v>
+        <v>22764.828999999991</v>
       </c>
       <c r="H23">
         <v>23176.20099999999</v>
@@ -1473,43 +1464,39 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>3055705945.167</v>
+        <v>3055705945.1669998</v>
       </c>
       <c r="M23">
-        <v>3027956090.311001</v>
+        <v>3027956090.3110008</v>
       </c>
       <c r="N23">
-        <v>3082766742.202999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>3082766742.2029991</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>3427.481</v>
+        <v>3427.4810000000002</v>
       </c>
       <c r="D24">
-        <v>3393.325999999999</v>
+        <v>3393.3259999999991</v>
       </c>
       <c r="E24">
-        <v>3460.939</v>
+        <v>3460.9389999999999</v>
       </c>
       <c r="F24">
-        <v>6742.198</v>
+        <v>6742.1980000000003</v>
       </c>
       <c r="G24">
-        <v>6659.329999999998</v>
+        <v>6659.3299999999981</v>
       </c>
       <c r="H24">
-        <v>6818.882000000001</v>
+        <v>6818.8820000000014</v>
       </c>
       <c r="I24">
         <v>134352859.447</v>
@@ -1518,46 +1505,42 @@
         <v>132996308.662</v>
       </c>
       <c r="K24">
-        <v>135672116.251</v>
+        <v>135672116.25099999</v>
       </c>
       <c r="L24">
-        <v>896673388.9800003</v>
+        <v>896673388.98000026</v>
       </c>
       <c r="M24">
-        <v>885663617.6069999</v>
+        <v>885663617.60699987</v>
       </c>
       <c r="N24">
-        <v>906923459.9980001</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>906923459.99800014</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>56574.95299999999</v>
+        <v>56574.952999999987</v>
       </c>
       <c r="D25">
-        <v>54311.811</v>
+        <v>54311.811000000002</v>
       </c>
       <c r="E25">
-        <v>58823.18899999999</v>
+        <v>58823.188999999991</v>
       </c>
       <c r="F25">
-        <v>534799.8970000001</v>
+        <v>534799.89700000011</v>
       </c>
       <c r="G25">
-        <v>524696.6359999999</v>
+        <v>524696.63599999994</v>
       </c>
       <c r="H25">
-        <v>544961.401</v>
+        <v>544961.40099999995</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1569,253 +1552,233 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>71130826465.38599</v>
+        <v>71130826465.385986</v>
       </c>
       <c r="M25">
-        <v>69777275933.69202</v>
+        <v>69777275933.692017</v>
       </c>
       <c r="N25">
-        <v>72481395219.66202</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>72481395219.662018</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>68137.34699999999</v>
+        <v>68137.346999999994</v>
       </c>
       <c r="D26">
-        <v>66346.747</v>
+        <v>66346.747000000003</v>
       </c>
       <c r="E26">
-        <v>69930.49499999997</v>
+        <v>69930.494999999966</v>
       </c>
       <c r="F26">
         <v>223908.302</v>
       </c>
       <c r="G26">
-        <v>218639.955</v>
+        <v>218639.95499999999</v>
       </c>
       <c r="H26">
-        <v>229210.192</v>
+        <v>229210.19200000001</v>
       </c>
       <c r="I26">
-        <v>868427452.1440001</v>
+        <v>868427452.14400005</v>
       </c>
       <c r="J26">
-        <v>844630696.603</v>
+        <v>844630696.60300004</v>
       </c>
       <c r="K26">
         <v>892156524.9289999</v>
       </c>
       <c r="L26">
-        <v>29780801550.84601</v>
+        <v>29780801550.846008</v>
       </c>
       <c r="M26">
-        <v>29074996676.675</v>
+        <v>29074996676.674999</v>
       </c>
       <c r="N26">
-        <v>30478320149.719</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>30478320149.719002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>61616.71799999999</v>
+        <v>61616.717999999993</v>
       </c>
       <c r="D27">
-        <v>60311.12199999999</v>
+        <v>60311.121999999988</v>
       </c>
       <c r="E27">
-        <v>62907.54299999999</v>
+        <v>62907.542999999991</v>
       </c>
       <c r="F27">
-        <v>230647.368</v>
+        <v>230647.36799999999</v>
       </c>
       <c r="G27">
-        <v>226735.3210000001</v>
+        <v>226735.32100000011</v>
       </c>
       <c r="H27">
-        <v>234532.207</v>
+        <v>234532.20699999999</v>
       </c>
       <c r="I27">
-        <v>763221218.6529999</v>
+        <v>763221218.65299988</v>
       </c>
       <c r="J27">
-        <v>748778141.734</v>
+        <v>748778141.73399997</v>
       </c>
       <c r="K27">
-        <v>777479547.2279996</v>
+        <v>777479547.22799957</v>
       </c>
       <c r="L27">
-        <v>30675565926.78799</v>
+        <v>30675565926.787991</v>
       </c>
       <c r="M27">
         <v>30153013325.48999</v>
       </c>
       <c r="N27">
-        <v>31200051313.052</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>31200051313.051998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
         <v>48201.462</v>
       </c>
       <c r="D28">
-        <v>47376.268</v>
+        <v>47376.267999999996</v>
       </c>
       <c r="E28">
-        <v>49017.31399999998</v>
+        <v>49017.313999999977</v>
       </c>
       <c r="F28">
         <v>168130.24</v>
       </c>
       <c r="G28">
-        <v>165570.415</v>
+        <v>165570.41500000001</v>
       </c>
       <c r="H28">
-        <v>170700.118</v>
+        <v>170700.11799999999</v>
       </c>
       <c r="I28">
-        <v>541003394.0489998</v>
+        <v>541003394.04899979</v>
       </c>
       <c r="J28">
-        <v>531659319.9010003</v>
+        <v>531659319.90100032</v>
       </c>
       <c r="K28">
-        <v>550297865.194</v>
+        <v>550297865.19400001</v>
       </c>
       <c r="L28">
-        <v>22363398383.302</v>
+        <v>22363398383.301998</v>
       </c>
       <c r="M28">
-        <v>22020889346.177</v>
+        <v>22020889346.176998</v>
       </c>
       <c r="N28">
         <v>22704544312.702</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
         <v>177955.527</v>
       </c>
       <c r="D29">
-        <v>174034.137</v>
+        <v>174034.13699999999</v>
       </c>
       <c r="E29">
         <v>181855.3520000001</v>
       </c>
       <c r="F29">
-        <v>622685.9099999995</v>
+        <v>622685.90999999945</v>
       </c>
       <c r="G29">
-        <v>610945.691</v>
+        <v>610945.69099999999</v>
       </c>
       <c r="H29">
-        <v>634442.517</v>
+        <v>634442.51699999999</v>
       </c>
       <c r="I29">
-        <v>2172652064.846002</v>
+        <v>2172652064.8460021</v>
       </c>
       <c r="J29">
         <v>2125068158.237999</v>
       </c>
       <c r="K29">
-        <v>2219933937.351001</v>
+        <v>2219933937.3510008</v>
       </c>
       <c r="L29">
-        <v>82819765860.93596</v>
+        <v>82819765860.935959</v>
       </c>
       <c r="M29">
         <v>81248899348.34198</v>
       </c>
       <c r="N29">
-        <v>84382915775.47302</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chronic diseases</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>84382915775.473022</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>52291.50199999999</v>
+        <v>52291.501999999993</v>
       </c>
       <c r="D30">
-        <v>51078.26299999999</v>
+        <v>51078.262999999992</v>
       </c>
       <c r="E30">
         <v>53492.37999999999</v>
       </c>
       <c r="F30">
-        <v>64910.33300000003</v>
+        <v>64910.333000000028</v>
       </c>
       <c r="G30">
-        <v>63484.226</v>
+        <v>63484.226000000002</v>
       </c>
       <c r="H30">
-        <v>66304.91500000002</v>
+        <v>66304.915000000023</v>
       </c>
       <c r="I30">
-        <v>2172652064.846002</v>
+        <v>2172652064.8460021</v>
       </c>
       <c r="J30">
         <v>2125068158.237999</v>
       </c>
       <c r="K30">
-        <v>2219933937.351001</v>
+        <v>2219933937.3510008</v>
       </c>
       <c r="L30">
-        <v>8633233450.382999</v>
+        <v>8633233450.3829994</v>
       </c>
       <c r="M30">
-        <v>8443667324.338997</v>
+        <v>8443667324.3389969</v>
       </c>
       <c r="N30">
-        <v>8818753813.608</v>
+        <v>8818753813.6079998</v>
       </c>
     </row>
   </sheetData>
